--- a/crypto_compare/output/l2_comparison.xlsx
+++ b/crypto_compare/output/l2_comparison.xlsx
@@ -416,26 +416,26 @@
     <xf numFmtId="164" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf numFmtId="3" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
@@ -492,8 +492,8 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -644,6 +644,12 @@
 комиссии за 365 дн (Arbitrum)</t>
       </text>
     </comment>
+    <comment ref="J5" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C6" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -684,6 +690,12 @@
 комиссии за 365 дн (OP Mainnet)</t>
       </text>
     </comment>
+    <comment ref="J6" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="E7" authorId="0" shapeId="0">
       <text>
         <t>DeFiLlama, 30.09.2026
@@ -714,6 +726,12 @@
 комиссии за 365 дн (Base)</t>
       </text>
     </comment>
+    <comment ref="J7" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C8" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -754,6 +772,12 @@
 комиссии за 365 дн (Mantle)</t>
       </text>
     </comment>
+    <comment ref="J8" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C9" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -794,6 +818,12 @@
 комиссии за 365 дн (Starknet)</t>
       </text>
     </comment>
+    <comment ref="J9" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C10" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -834,6 +864,12 @@
 комиссии за 365 дн (ZKsync Era)</t>
       </text>
     </comment>
+    <comment ref="J10" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C11" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -874,6 +910,12 @@
 комиссии за 365 дн (Linea)</t>
       </text>
     </comment>
+    <comment ref="J11" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C12" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -912,6 +954,12 @@
       <text>
         <t>DeFiLlama, 30.09.2026
 комиссии за 365 дн (Scroll)</t>
+      </text>
+    </comment>
+    <comment ref="J12" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
       </text>
     </comment>
   </commentList>
@@ -1310,13 +1358,13 @@
         </is>
       </c>
       <c r="C5" s="44" t="n">
-        <v>1372.064196</v>
+        <v>1391.300683</v>
       </c>
       <c r="D5" s="44" t="n">
-        <v>2022.030964</v>
+        <v>2050.380054</v>
       </c>
       <c r="E5" s="44" t="n">
-        <v>1440.362091</v>
+        <v>1424.891626</v>
       </c>
       <c r="F5" s="44" t="n">
         <v>1926.991061</v>
@@ -1330,34 +1378,36 @@
       <c r="I5" s="45" t="n">
         <v>10.394479</v>
       </c>
-      <c r="J5" s="46" t="n"/>
-      <c r="K5" s="47" t="n"/>
-      <c r="L5" s="48" t="n"/>
-      <c r="M5" s="49">
+      <c r="J5" s="44" t="n">
+        <v>166</v>
+      </c>
+      <c r="K5" s="46" t="n"/>
+      <c r="L5" s="47" t="n"/>
+      <c r="M5" s="48">
         <f>IF(OR(E5="",F5="",F5=0),"",E5/F5-1)</f>
         <v/>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="48">
         <f>IF(OR(G5="",H5="",H5=0),"",G5/H5-1)</f>
         <v/>
       </c>
-      <c r="O5" s="50">
+      <c r="O5" s="49">
         <f>IF(OR(C5="",E5="",E5=0),"",C5/E5)</f>
         <v/>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="50">
         <f>IF(OR(C5="",I5="",I5=0),"",C5/I5)</f>
         <v/>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="49">
         <f>IF(OR(C5="",D5="",C5=0),"",D5/C5)</f>
         <v/>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="51">
         <f>Расчёт!K5</f>
         <v/>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="51">
         <f>IF(R5="","",RANK(R5,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1374,13 +1424,13 @@
         </is>
       </c>
       <c r="C6" s="44" t="n">
-        <v>299.601738</v>
+        <v>302.486561</v>
       </c>
       <c r="D6" s="44" t="n">
-        <v>559.56066</v>
+        <v>564.94859</v>
       </c>
       <c r="E6" s="44" t="n">
-        <v>488.953651</v>
+        <v>487.462878</v>
       </c>
       <c r="F6" s="44" t="n">
         <v>195.624571</v>
@@ -1394,34 +1444,36 @@
       <c r="I6" s="45" t="n">
         <v>1.163975</v>
       </c>
-      <c r="J6" s="46" t="n"/>
-      <c r="K6" s="47" t="n"/>
-      <c r="L6" s="48" t="n"/>
-      <c r="M6" s="49">
+      <c r="J6" s="44" t="n">
+        <v>147</v>
+      </c>
+      <c r="K6" s="46" t="n"/>
+      <c r="L6" s="47" t="n"/>
+      <c r="M6" s="48">
         <f>IF(OR(E6="",F6="",F6=0),"",E6/F6-1)</f>
         <v/>
       </c>
-      <c r="N6" s="49">
+      <c r="N6" s="48">
         <f>IF(OR(G6="",H6="",H6=0),"",G6/H6-1)</f>
         <v/>
       </c>
-      <c r="O6" s="50">
+      <c r="O6" s="49">
         <f>IF(OR(C6="",E6="",E6=0),"",C6/E6)</f>
         <v/>
       </c>
-      <c r="P6" s="51">
+      <c r="P6" s="50">
         <f>IF(OR(C6="",I6="",I6=0),"",C6/I6)</f>
         <v/>
       </c>
-      <c r="Q6" s="50">
+      <c r="Q6" s="49">
         <f>IF(OR(C6="",D6="",C6=0),"",D6/C6)</f>
         <v/>
       </c>
-      <c r="R6" s="52">
+      <c r="R6" s="51">
         <f>Расчёт!K6</f>
         <v/>
       </c>
-      <c r="S6" s="52">
+      <c r="S6" s="51">
         <f>IF(R6="","",RANK(R6,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1437,10 +1489,10 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="C7" s="46" t="n"/>
-      <c r="D7" s="46" t="n"/>
+      <c r="C7" s="52" t="n"/>
+      <c r="D7" s="52" t="n"/>
       <c r="E7" s="44" t="n">
-        <v>6361.888402</v>
+        <v>6284.712317</v>
       </c>
       <c r="F7" s="44" t="n">
         <v>4057.366831</v>
@@ -1454,34 +1506,36 @@
       <c r="I7" s="45" t="n">
         <v>56.624755</v>
       </c>
-      <c r="J7" s="46" t="n"/>
-      <c r="K7" s="47" t="n"/>
-      <c r="L7" s="48" t="n"/>
-      <c r="M7" s="49">
+      <c r="J7" s="44" t="n">
+        <v>172</v>
+      </c>
+      <c r="K7" s="46" t="n"/>
+      <c r="L7" s="47" t="n"/>
+      <c r="M7" s="48">
         <f>IF(OR(E7="",F7="",F7=0),"",E7/F7-1)</f>
         <v/>
       </c>
-      <c r="N7" s="49">
+      <c r="N7" s="48">
         <f>IF(OR(G7="",H7="",H7=0),"",G7/H7-1)</f>
         <v/>
       </c>
-      <c r="O7" s="50">
+      <c r="O7" s="49">
         <f>IF(OR(C7="",E7="",E7=0),"",C7/E7)</f>
         <v/>
       </c>
-      <c r="P7" s="51">
+      <c r="P7" s="50">
         <f>IF(OR(C7="",I7="",I7=0),"",C7/I7)</f>
         <v/>
       </c>
-      <c r="Q7" s="50">
+      <c r="Q7" s="49">
         <f>IF(OR(C7="",D7="",C7=0),"",D7/C7)</f>
         <v/>
       </c>
-      <c r="R7" s="52">
+      <c r="R7" s="51">
         <f>Расчёт!K7</f>
         <v/>
       </c>
-      <c r="S7" s="52">
+      <c r="S7" s="51">
         <f>IF(R7="","",RANK(R7,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1498,13 +1552,13 @@
         </is>
       </c>
       <c r="C8" s="44" t="n">
-        <v>2303.632024</v>
+        <v>2299.943263</v>
       </c>
       <c r="D8" s="44" t="n">
-        <v>4338.503984</v>
+        <v>4331.556822</v>
       </c>
       <c r="E8" s="44" t="n">
-        <v>105.989362</v>
+        <v>105.676763</v>
       </c>
       <c r="F8" s="44" t="n">
         <v>653.480331</v>
@@ -1518,34 +1572,36 @@
       <c r="I8" s="45" t="n">
         <v>0.252569</v>
       </c>
-      <c r="J8" s="46" t="n"/>
-      <c r="K8" s="47" t="n"/>
-      <c r="L8" s="48" t="n"/>
-      <c r="M8" s="49">
+      <c r="J8" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" s="46" t="n"/>
+      <c r="L8" s="47" t="n"/>
+      <c r="M8" s="48">
         <f>IF(OR(E8="",F8="",F8=0),"",E8/F8-1)</f>
         <v/>
       </c>
-      <c r="N8" s="49">
+      <c r="N8" s="48">
         <f>IF(OR(G8="",H8="",H8=0),"",G8/H8-1)</f>
         <v/>
       </c>
-      <c r="O8" s="50">
+      <c r="O8" s="49">
         <f>IF(OR(C8="",E8="",E8=0),"",C8/E8)</f>
         <v/>
       </c>
-      <c r="P8" s="51">
+      <c r="P8" s="50">
         <f>IF(OR(C8="",I8="",I8=0),"",C8/I8)</f>
         <v/>
       </c>
-      <c r="Q8" s="50">
+      <c r="Q8" s="49">
         <f>IF(OR(C8="",D8="",C8=0),"",D8/C8)</f>
         <v/>
       </c>
-      <c r="R8" s="52">
+      <c r="R8" s="51">
         <f>Расчёт!K8</f>
         <v/>
       </c>
-      <c r="S8" s="52">
+      <c r="S8" s="51">
         <f>IF(R8="","",RANK(R8,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1562,13 +1618,13 @@
         </is>
       </c>
       <c r="C9" s="44" t="n">
-        <v>303.738166</v>
+        <v>309.25731</v>
       </c>
       <c r="D9" s="44" t="n">
-        <v>413.21516</v>
+        <v>420.72358</v>
       </c>
       <c r="E9" s="44" t="n">
-        <v>156.177773</v>
+        <v>155.859514</v>
       </c>
       <c r="F9" s="44" t="n">
         <v>246.803376</v>
@@ -1582,34 +1638,36 @@
       <c r="I9" s="45" t="n">
         <v>1.990909</v>
       </c>
-      <c r="J9" s="46" t="n"/>
-      <c r="K9" s="47" t="n"/>
-      <c r="L9" s="48" t="n"/>
-      <c r="M9" s="49">
+      <c r="J9" s="44" t="n">
+        <v>141</v>
+      </c>
+      <c r="K9" s="46" t="n"/>
+      <c r="L9" s="47" t="n"/>
+      <c r="M9" s="48">
         <f>IF(OR(E9="",F9="",F9=0),"",E9/F9-1)</f>
         <v/>
       </c>
-      <c r="N9" s="49">
+      <c r="N9" s="48">
         <f>IF(OR(G9="",H9="",H9=0),"",G9/H9-1)</f>
         <v/>
       </c>
-      <c r="O9" s="50">
+      <c r="O9" s="49">
         <f>IF(OR(C9="",E9="",E9=0),"",C9/E9)</f>
         <v/>
       </c>
-      <c r="P9" s="51">
+      <c r="P9" s="50">
         <f>IF(OR(C9="",I9="",I9=0),"",C9/I9)</f>
         <v/>
       </c>
-      <c r="Q9" s="50">
+      <c r="Q9" s="49">
         <f>IF(OR(C9="",D9="",C9=0),"",D9/C9)</f>
         <v/>
       </c>
-      <c r="R9" s="52">
+      <c r="R9" s="51">
         <f>Расчёт!K9</f>
         <v/>
       </c>
-      <c r="S9" s="52">
+      <c r="S9" s="51">
         <f>IF(R9="","",RANK(R9,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1626,13 +1684,13 @@
         </is>
       </c>
       <c r="C10" s="44" t="n">
-        <v>131.74708</v>
+        <v>133.005981</v>
       </c>
       <c r="D10" s="44" t="n">
-        <v>255.783171</v>
+        <v>258.227292</v>
       </c>
       <c r="E10" s="44" t="n">
-        <v>15.90072</v>
+        <v>15.747885</v>
       </c>
       <c r="F10" s="44" t="n">
         <v>22.377373</v>
@@ -1646,34 +1704,36 @@
       <c r="I10" s="45" t="n">
         <v>0.498537</v>
       </c>
-      <c r="J10" s="46" t="n"/>
-      <c r="K10" s="47" t="n"/>
-      <c r="L10" s="48" t="n"/>
-      <c r="M10" s="49">
+      <c r="J10" s="44" t="n">
+        <v>73</v>
+      </c>
+      <c r="K10" s="46" t="n"/>
+      <c r="L10" s="47" t="n"/>
+      <c r="M10" s="48">
         <f>IF(OR(E10="",F10="",F10=0),"",E10/F10-1)</f>
         <v/>
       </c>
-      <c r="N10" s="49">
+      <c r="N10" s="48">
         <f>IF(OR(G10="",H10="",H10=0),"",G10/H10-1)</f>
         <v/>
       </c>
-      <c r="O10" s="50">
+      <c r="O10" s="49">
         <f>IF(OR(C10="",E10="",E10=0),"",C10/E10)</f>
         <v/>
       </c>
-      <c r="P10" s="51">
+      <c r="P10" s="50">
         <f>IF(OR(C10="",I10="",I10=0),"",C10/I10)</f>
         <v/>
       </c>
-      <c r="Q10" s="50">
+      <c r="Q10" s="49">
         <f>IF(OR(C10="",D10="",C10=0),"",D10/C10)</f>
         <v/>
       </c>
-      <c r="R10" s="52">
+      <c r="R10" s="51">
         <f>Расчёт!K10</f>
         <v/>
       </c>
-      <c r="S10" s="52">
+      <c r="S10" s="51">
         <f>IF(R10="","",RANK(R10,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1690,13 +1750,13 @@
         </is>
       </c>
       <c r="C11" s="44" t="n">
-        <v>72.124611</v>
+        <v>72.779487</v>
       </c>
       <c r="D11" s="44" t="n">
-        <v>210.529409</v>
+        <v>212.440969</v>
       </c>
       <c r="E11" s="44" t="n">
-        <v>26.660603</v>
+        <v>26.282442</v>
       </c>
       <c r="F11" s="44" t="n">
         <v>92.46676100000001</v>
@@ -1710,34 +1770,36 @@
       <c r="I11" s="45" t="n">
         <v>1.347858</v>
       </c>
-      <c r="J11" s="46" t="n"/>
-      <c r="K11" s="47" t="n"/>
-      <c r="L11" s="48" t="n"/>
-      <c r="M11" s="49">
+      <c r="J11" s="44" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" s="46" t="n"/>
+      <c r="L11" s="47" t="n"/>
+      <c r="M11" s="48">
         <f>IF(OR(E11="",F11="",F11=0),"",E11/F11-1)</f>
         <v/>
       </c>
-      <c r="N11" s="49">
+      <c r="N11" s="48">
         <f>IF(OR(G11="",H11="",H11=0),"",G11/H11-1)</f>
         <v/>
       </c>
-      <c r="O11" s="50">
+      <c r="O11" s="49">
         <f>IF(OR(C11="",E11="",E11=0),"",C11/E11)</f>
         <v/>
       </c>
-      <c r="P11" s="51">
+      <c r="P11" s="50">
         <f>IF(OR(C11="",I11="",I11=0),"",C11/I11)</f>
         <v/>
       </c>
-      <c r="Q11" s="50">
+      <c r="Q11" s="49">
         <f>IF(OR(C11="",D11="",C11=0),"",D11/C11)</f>
         <v/>
       </c>
-      <c r="R11" s="52">
+      <c r="R11" s="51">
         <f>Расчёт!K11</f>
         <v/>
       </c>
-      <c r="S11" s="52">
+      <c r="S11" s="51">
         <f>IF(R11="","",RANK(R11,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1754,13 +1816,13 @@
         </is>
       </c>
       <c r="C12" s="44" t="n">
-        <v>4.688116</v>
+        <v>4.739309</v>
       </c>
       <c r="D12" s="44" t="n">
-        <v>24.674296</v>
+        <v>24.94373</v>
       </c>
       <c r="E12" s="53" t="n">
-        <v>9.206047</v>
+        <v>9.169048</v>
       </c>
       <c r="F12" s="44" t="n">
         <v>228.115291</v>
@@ -1774,34 +1836,36 @@
       <c r="I12" s="45" t="n">
         <v>0.248046</v>
       </c>
-      <c r="J12" s="46" t="n"/>
-      <c r="K12" s="47" t="n"/>
-      <c r="L12" s="48" t="n"/>
-      <c r="M12" s="49">
+      <c r="J12" s="44" t="n">
+        <v>16</v>
+      </c>
+      <c r="K12" s="46" t="n"/>
+      <c r="L12" s="47" t="n"/>
+      <c r="M12" s="48">
         <f>IF(OR(E12="",F12="",F12=0),"",E12/F12-1)</f>
         <v/>
       </c>
-      <c r="N12" s="49">
+      <c r="N12" s="48">
         <f>IF(OR(G12="",H12="",H12=0),"",G12/H12-1)</f>
         <v/>
       </c>
-      <c r="O12" s="50">
+      <c r="O12" s="49">
         <f>IF(OR(C12="",E12="",E12=0),"",C12/E12)</f>
         <v/>
       </c>
-      <c r="P12" s="51">
+      <c r="P12" s="50">
         <f>IF(OR(C12="",I12="",I12=0),"",C12/I12)</f>
         <v/>
       </c>
-      <c r="Q12" s="50">
+      <c r="Q12" s="49">
         <f>IF(OR(C12="",D12="",C12=0),"",D12/C12)</f>
         <v/>
       </c>
-      <c r="R12" s="52">
+      <c r="R12" s="51">
         <f>Расчёт!K12</f>
         <v/>
       </c>
-      <c r="S12" s="52">
+      <c r="S12" s="51">
         <f>IF(R12="","",RANK(R12,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1809,41 +1873,41 @@
     <row r="13" ht="15" customHeight="1" s="34">
       <c r="A13" s="42" t="n"/>
       <c r="B13" s="43" t="n"/>
-      <c r="C13" s="46" t="n"/>
-      <c r="D13" s="46" t="n"/>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
-      <c r="H13" s="46" t="n"/>
+      <c r="C13" s="52" t="n"/>
+      <c r="D13" s="52" t="n"/>
+      <c r="E13" s="52" t="n"/>
+      <c r="F13" s="52" t="n"/>
+      <c r="G13" s="52" t="n"/>
+      <c r="H13" s="52" t="n"/>
       <c r="I13" s="54" t="n"/>
-      <c r="J13" s="46" t="n"/>
-      <c r="K13" s="47" t="n"/>
-      <c r="L13" s="48" t="n"/>
-      <c r="M13" s="49">
+      <c r="J13" s="52" t="n"/>
+      <c r="K13" s="46" t="n"/>
+      <c r="L13" s="47" t="n"/>
+      <c r="M13" s="48">
         <f>IF(OR(E13="",F13="",F13=0),"",E13/F13-1)</f>
         <v/>
       </c>
-      <c r="N13" s="49">
+      <c r="N13" s="48">
         <f>IF(OR(G13="",H13="",H13=0),"",G13/H13-1)</f>
         <v/>
       </c>
-      <c r="O13" s="50">
+      <c r="O13" s="49">
         <f>IF(OR(C13="",E13="",E13=0),"",C13/E13)</f>
         <v/>
       </c>
-      <c r="P13" s="51">
+      <c r="P13" s="50">
         <f>IF(OR(C13="",I13="",I13=0),"",C13/I13)</f>
         <v/>
       </c>
-      <c r="Q13" s="50">
+      <c r="Q13" s="49">
         <f>IF(OR(C13="",D13="",C13=0),"",D13/C13)</f>
         <v/>
       </c>
-      <c r="R13" s="52">
+      <c r="R13" s="51">
         <f>Расчёт!K13</f>
         <v/>
       </c>
-      <c r="S13" s="52">
+      <c r="S13" s="51">
         <f>IF(R13="","",RANK(R13,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1851,41 +1915,41 @@
     <row r="14" ht="15" customHeight="1" s="34">
       <c r="A14" s="42" t="n"/>
       <c r="B14" s="43" t="n"/>
-      <c r="C14" s="46" t="n"/>
-      <c r="D14" s="46" t="n"/>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-      <c r="H14" s="46" t="n"/>
+      <c r="C14" s="52" t="n"/>
+      <c r="D14" s="52" t="n"/>
+      <c r="E14" s="52" t="n"/>
+      <c r="F14" s="52" t="n"/>
+      <c r="G14" s="52" t="n"/>
+      <c r="H14" s="52" t="n"/>
       <c r="I14" s="54" t="n"/>
-      <c r="J14" s="46" t="n"/>
-      <c r="K14" s="47" t="n"/>
-      <c r="L14" s="48" t="n"/>
-      <c r="M14" s="49">
+      <c r="J14" s="52" t="n"/>
+      <c r="K14" s="46" t="n"/>
+      <c r="L14" s="47" t="n"/>
+      <c r="M14" s="48">
         <f>IF(OR(E14="",F14="",F14=0),"",E14/F14-1)</f>
         <v/>
       </c>
-      <c r="N14" s="49">
+      <c r="N14" s="48">
         <f>IF(OR(G14="",H14="",H14=0),"",G14/H14-1)</f>
         <v/>
       </c>
-      <c r="O14" s="50">
+      <c r="O14" s="49">
         <f>IF(OR(C14="",E14="",E14=0),"",C14/E14)</f>
         <v/>
       </c>
-      <c r="P14" s="51">
+      <c r="P14" s="50">
         <f>IF(OR(C14="",I14="",I14=0),"",C14/I14)</f>
         <v/>
       </c>
-      <c r="Q14" s="50">
+      <c r="Q14" s="49">
         <f>IF(OR(C14="",D14="",C14=0),"",D14/C14)</f>
         <v/>
       </c>
-      <c r="R14" s="52">
+      <c r="R14" s="51">
         <f>Расчёт!K14</f>
         <v/>
       </c>
-      <c r="S14" s="52">
+      <c r="S14" s="51">
         <f>IF(R14="","",RANK(R14,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -3870,7 +3934,7 @@
         </is>
       </c>
       <c r="C4" s="72" t="n">
-        <v>1372.064196</v>
+        <v>1391.300683</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3891,7 +3955,7 @@
         </is>
       </c>
       <c r="C5" s="72" t="n">
-        <v>2022.030964</v>
+        <v>2050.380054</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3912,7 +3976,7 @@
         </is>
       </c>
       <c r="C6" s="72" t="n">
-        <v>1440.362091</v>
+        <v>1424.891626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4026,23 +4090,29 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="73" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Arbitrum</t>
         </is>
       </c>
-      <c r="B11" s="73" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C11" s="74" t="n"/>
-      <c r="D11" s="73" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E11" s="73" t="inlineStr"/>
+      <c r="C11" s="72" t="n">
+        <v>166</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="73" t="inlineStr">
@@ -4055,7 +4125,7 @@
           <t>Разлок за 6 мес, % предложения</t>
         </is>
       </c>
-      <c r="C12" s="75" t="n"/>
+      <c r="C12" s="74" t="n"/>
       <c r="D12" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -4074,7 +4144,7 @@
           <t>Инвесторы и команда, 1–5</t>
         </is>
       </c>
-      <c r="C13" s="74" t="n"/>
+      <c r="C13" s="75" t="n"/>
       <c r="D13" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -4094,7 +4164,7 @@
         </is>
       </c>
       <c r="C14" s="72" t="n">
-        <v>299.601738</v>
+        <v>302.486561</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4115,7 +4185,7 @@
         </is>
       </c>
       <c r="C15" s="72" t="n">
-        <v>559.56066</v>
+        <v>564.94859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4136,7 +4206,7 @@
         </is>
       </c>
       <c r="C16" s="72" t="n">
-        <v>488.953651</v>
+        <v>487.462878</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4250,23 +4320,29 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="73" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Optimism</t>
         </is>
       </c>
-      <c r="B21" s="73" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C21" s="74" t="n"/>
-      <c r="D21" s="73" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E21" s="73" t="inlineStr"/>
+      <c r="C21" s="72" t="n">
+        <v>147</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="73" t="inlineStr">
@@ -4279,7 +4355,7 @@
           <t>Разлок за 6 мес, % предложения</t>
         </is>
       </c>
-      <c r="C22" s="75" t="n"/>
+      <c r="C22" s="74" t="n"/>
       <c r="D22" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -4298,7 +4374,7 @@
           <t>Инвесторы и команда, 1–5</t>
         </is>
       </c>
-      <c r="C23" s="74" t="n"/>
+      <c r="C23" s="75" t="n"/>
       <c r="D23" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -4317,7 +4393,7 @@
           <t>Капитализация, $ млн</t>
         </is>
       </c>
-      <c r="C24" s="74" t="n"/>
+      <c r="C24" s="75" t="n"/>
       <c r="D24" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -4336,7 +4412,7 @@
           <t>FDV, $ млн</t>
         </is>
       </c>
-      <c r="C25" s="74" t="n"/>
+      <c r="C25" s="75" t="n"/>
       <c r="D25" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -4356,7 +4432,7 @@
         </is>
       </c>
       <c r="C26" s="72" t="n">
-        <v>6361.888402</v>
+        <v>6284.712317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4470,23 +4546,29 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="73" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="B31" s="73" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C31" s="74" t="n"/>
-      <c r="D31" s="73" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E31" s="73" t="inlineStr"/>
+      <c r="C31" s="72" t="n">
+        <v>172</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="73" t="inlineStr">
@@ -4499,7 +4581,7 @@
           <t>Разлок за 6 мес, % предложения</t>
         </is>
       </c>
-      <c r="C32" s="75" t="n"/>
+      <c r="C32" s="74" t="n"/>
       <c r="D32" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -4518,7 +4600,7 @@
           <t>Инвесторы и команда, 1–5</t>
         </is>
       </c>
-      <c r="C33" s="74" t="n"/>
+      <c r="C33" s="75" t="n"/>
       <c r="D33" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -4538,7 +4620,7 @@
         </is>
       </c>
       <c r="C34" s="72" t="n">
-        <v>2303.632024</v>
+        <v>2299.943263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4559,7 +4641,7 @@
         </is>
       </c>
       <c r="C35" s="72" t="n">
-        <v>4338.503984</v>
+        <v>4331.556822</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4580,7 +4662,7 @@
         </is>
       </c>
       <c r="C36" s="72" t="n">
-        <v>105.989362</v>
+        <v>105.676763</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4694,23 +4776,29 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="73" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Mantle</t>
         </is>
       </c>
-      <c r="B41" s="73" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C41" s="74" t="n"/>
-      <c r="D41" s="73" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E41" s="73" t="inlineStr"/>
+      <c r="C41" s="72" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="73" t="inlineStr">
@@ -4723,7 +4811,7 @@
           <t>Разлок за 6 мес, % предложения</t>
         </is>
       </c>
-      <c r="C42" s="75" t="n"/>
+      <c r="C42" s="74" t="n"/>
       <c r="D42" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -4742,7 +4830,7 @@
           <t>Инвесторы и команда, 1–5</t>
         </is>
       </c>
-      <c r="C43" s="74" t="n"/>
+      <c r="C43" s="75" t="n"/>
       <c r="D43" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -4762,7 +4850,7 @@
         </is>
       </c>
       <c r="C44" s="72" t="n">
-        <v>303.738166</v>
+        <v>309.25731</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4783,7 +4871,7 @@
         </is>
       </c>
       <c r="C45" s="72" t="n">
-        <v>413.21516</v>
+        <v>420.72358</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4804,7 +4892,7 @@
         </is>
       </c>
       <c r="C46" s="72" t="n">
-        <v>156.177773</v>
+        <v>155.859514</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4918,23 +5006,29 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="73" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Starknet</t>
         </is>
       </c>
-      <c r="B51" s="73" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C51" s="74" t="n"/>
-      <c r="D51" s="73" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E51" s="73" t="inlineStr"/>
+      <c r="C51" s="72" t="n">
+        <v>141</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="73" t="inlineStr">
@@ -4947,7 +5041,7 @@
           <t>Разлок за 6 мес, % предложения</t>
         </is>
       </c>
-      <c r="C52" s="75" t="n"/>
+      <c r="C52" s="74" t="n"/>
       <c r="D52" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -4966,7 +5060,7 @@
           <t>Инвесторы и команда, 1–5</t>
         </is>
       </c>
-      <c r="C53" s="74" t="n"/>
+      <c r="C53" s="75" t="n"/>
       <c r="D53" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -4986,7 +5080,7 @@
         </is>
       </c>
       <c r="C54" s="72" t="n">
-        <v>131.74708</v>
+        <v>133.005981</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5007,7 +5101,7 @@
         </is>
       </c>
       <c r="C55" s="72" t="n">
-        <v>255.783171</v>
+        <v>258.227292</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5028,7 +5122,7 @@
         </is>
       </c>
       <c r="C56" s="72" t="n">
-        <v>15.90072</v>
+        <v>15.747885</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5142,23 +5236,29 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="73" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>ZKsync</t>
         </is>
       </c>
-      <c r="B61" s="73" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C61" s="74" t="n"/>
-      <c r="D61" s="73" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E61" s="73" t="inlineStr"/>
+      <c r="C61" s="72" t="n">
+        <v>73</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="73" t="inlineStr">
@@ -5171,7 +5271,7 @@
           <t>Разлок за 6 мес, % предложения</t>
         </is>
       </c>
-      <c r="C62" s="75" t="n"/>
+      <c r="C62" s="74" t="n"/>
       <c r="D62" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -5190,7 +5290,7 @@
           <t>Инвесторы и команда, 1–5</t>
         </is>
       </c>
-      <c r="C63" s="74" t="n"/>
+      <c r="C63" s="75" t="n"/>
       <c r="D63" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -5210,7 +5310,7 @@
         </is>
       </c>
       <c r="C64" s="72" t="n">
-        <v>72.124611</v>
+        <v>72.779487</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5231,7 +5331,7 @@
         </is>
       </c>
       <c r="C65" s="72" t="n">
-        <v>210.529409</v>
+        <v>212.440969</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5252,7 +5352,7 @@
         </is>
       </c>
       <c r="C66" s="72" t="n">
-        <v>26.660603</v>
+        <v>26.282442</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5366,23 +5466,29 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="73" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Linea</t>
         </is>
       </c>
-      <c r="B71" s="73" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C71" s="74" t="n"/>
-      <c r="D71" s="73" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E71" s="73" t="inlineStr"/>
+      <c r="C71" s="72" t="n">
+        <v>7</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="73" t="inlineStr">
@@ -5395,7 +5501,7 @@
           <t>Разлок за 6 мес, % предложения</t>
         </is>
       </c>
-      <c r="C72" s="75" t="n"/>
+      <c r="C72" s="74" t="n"/>
       <c r="D72" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -5414,7 +5520,7 @@
           <t>Инвесторы и команда, 1–5</t>
         </is>
       </c>
-      <c r="C73" s="74" t="n"/>
+      <c r="C73" s="75" t="n"/>
       <c r="D73" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -5434,7 +5540,7 @@
         </is>
       </c>
       <c r="C74" s="72" t="n">
-        <v>4.688116</v>
+        <v>4.739309</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5455,7 +5561,7 @@
         </is>
       </c>
       <c r="C75" s="72" t="n">
-        <v>24.674296</v>
+        <v>24.94373</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5476,7 +5582,7 @@
         </is>
       </c>
       <c r="C76" s="77" t="n">
-        <v>9.206047</v>
+        <v>9.169048</v>
       </c>
       <c r="D76" s="76" t="inlineStr">
         <is>
@@ -5590,23 +5696,29 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="73" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Scroll</t>
         </is>
       </c>
-      <c r="B81" s="73" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C81" s="74" t="n"/>
-      <c r="D81" s="73" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E81" s="73" t="inlineStr"/>
+      <c r="C81" s="72" t="n">
+        <v>16</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="73" t="inlineStr">
@@ -5619,7 +5731,7 @@
           <t>Разлок за 6 мес, % предложения</t>
         </is>
       </c>
-      <c r="C82" s="75" t="n"/>
+      <c r="C82" s="74" t="n"/>
       <c r="D82" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
@@ -5638,7 +5750,7 @@
           <t>Инвесторы и команда, 1–5</t>
         </is>
       </c>
-      <c r="C83" s="74" t="n"/>
+      <c r="C83" s="75" t="n"/>
       <c r="D83" s="73" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
